--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/12.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/12.xlsx
@@ -426,13 +426,13 @@
         <v>-11.56979523343322</v>
       </c>
       <c r="E2">
-        <v>-17.57101105792749</v>
+        <v>-19.50657594675996</v>
       </c>
       <c r="F2">
-        <v>-3.104900928666462</v>
+        <v>-3.845690016172393</v>
       </c>
       <c r="G2">
-        <v>-12.07514688623355</v>
+        <v>-12.81514765964888</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.77217026362932</v>
       </c>
       <c r="E3">
-        <v>-17.91104511421544</v>
+        <v>-21.28675077849323</v>
       </c>
       <c r="F3">
-        <v>-3.216010676771363</v>
+        <v>-4.047979821038241</v>
       </c>
       <c r="G3">
-        <v>-11.97674633288736</v>
+        <v>-12.31134233896861</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.07068397030973</v>
       </c>
       <c r="E4">
-        <v>-18.36692659256761</v>
+        <v>-21.35393521887103</v>
       </c>
       <c r="F4">
-        <v>-3.147931301772285</v>
+        <v>-3.957267791859875</v>
       </c>
       <c r="G4">
-        <v>-11.56768300351451</v>
+        <v>-13.22571706971751</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.42117043530872</v>
       </c>
       <c r="E5">
-        <v>-19.0837659140858</v>
+        <v>-21.3602931963778</v>
       </c>
       <c r="F5">
-        <v>-3.179142528774965</v>
+        <v>-3.762130939517201</v>
       </c>
       <c r="G5">
-        <v>-11.78153661865132</v>
+        <v>-12.8546043489012</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.81486966462974</v>
       </c>
       <c r="E6">
-        <v>-19.33566680923647</v>
+        <v>-22.04704080811501</v>
       </c>
       <c r="F6">
-        <v>-3.028674560260852</v>
+        <v>-3.71826971390637</v>
       </c>
       <c r="G6">
-        <v>-11.63453789278819</v>
+        <v>-12.59372754759599</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.22252249445195</v>
       </c>
       <c r="E7">
-        <v>-20.00227176858757</v>
+        <v>-23.17141561947949</v>
       </c>
       <c r="F7">
-        <v>-3.037074205725239</v>
+        <v>-3.924469412913432</v>
       </c>
       <c r="G7">
-        <v>-11.63152573139662</v>
+        <v>-11.7039718222076</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.61538802051131</v>
       </c>
       <c r="E8">
-        <v>-20.48387497930331</v>
+        <v>-23.72258071942705</v>
       </c>
       <c r="F8">
-        <v>-2.788998049404454</v>
+        <v>-3.604039505795124</v>
       </c>
       <c r="G8">
-        <v>-11.27433195243547</v>
+        <v>-12.31242514208323</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.96275126294196</v>
       </c>
       <c r="E9">
-        <v>-21.12415139077382</v>
+        <v>-22.97977965642289</v>
       </c>
       <c r="F9">
-        <v>-2.749736747981369</v>
+        <v>-3.635840530388597</v>
       </c>
       <c r="G9">
-        <v>-11.54155135501509</v>
+        <v>-11.94423927089794</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.22853965049331</v>
       </c>
       <c r="E10">
-        <v>-22.27599139699481</v>
+        <v>-23.73434569489898</v>
       </c>
       <c r="F10">
-        <v>-2.443507543249253</v>
+        <v>-3.881134200603378</v>
       </c>
       <c r="G10">
-        <v>-11.02705909571572</v>
+        <v>-12.62178199192924</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-14.3900747724086</v>
       </c>
       <c r="E11">
-        <v>-22.47721413952564</v>
+        <v>-24.86519622409442</v>
       </c>
       <c r="F11">
-        <v>-2.598505853089277</v>
+        <v>-3.330077696504258</v>
       </c>
       <c r="G11">
-        <v>-10.87181466007371</v>
+        <v>-12.13414324987236</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-14.42603670015837</v>
       </c>
       <c r="E12">
-        <v>-22.60184680116475</v>
+        <v>-25.01736653617417</v>
       </c>
       <c r="F12">
-        <v>-2.644345220057993</v>
+        <v>-3.631476690910649</v>
       </c>
       <c r="G12">
-        <v>-10.58947210732661</v>
+        <v>-12.58136718598156</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-14.32483075673443</v>
       </c>
       <c r="E13">
-        <v>-22.43719148624585</v>
+        <v>-25.72717313755845</v>
       </c>
       <c r="F13">
-        <v>-2.614856997253136</v>
+        <v>-2.819791779236123</v>
       </c>
       <c r="G13">
-        <v>-9.980149263737726</v>
+        <v>-11.3155276891143</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.09059820571473</v>
       </c>
       <c r="E14">
-        <v>-24.11303480531641</v>
+        <v>-26.26930393186071</v>
       </c>
       <c r="F14">
-        <v>-2.450439321675879</v>
+        <v>-2.908234910098221</v>
       </c>
       <c r="G14">
-        <v>-9.352707514697588</v>
+        <v>-10.31328512622503</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-13.72974890009862</v>
       </c>
       <c r="E15">
-        <v>-24.70029637157911</v>
+        <v>-27.62902806587782</v>
       </c>
       <c r="F15">
-        <v>-1.973018052746412</v>
+        <v>-2.835894413179143</v>
       </c>
       <c r="G15">
-        <v>-8.863136133142199</v>
+        <v>-10.89790037147129</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-13.26809049148287</v>
       </c>
       <c r="E16">
-        <v>-25.67902640190889</v>
+        <v>-27.990450104904</v>
       </c>
       <c r="F16">
-        <v>-2.105584173318626</v>
+        <v>-2.763580424016954</v>
       </c>
       <c r="G16">
-        <v>-8.837693541170264</v>
+        <v>-10.76846274339432</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-12.72799498848308</v>
       </c>
       <c r="E17">
-        <v>-26.62631523720342</v>
+        <v>-28.52147255246545</v>
       </c>
       <c r="F17">
-        <v>-1.935301656529548</v>
+        <v>-2.704302452672621</v>
       </c>
       <c r="G17">
-        <v>-8.136384932383908</v>
+        <v>-10.87406229684193</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-12.1411181675394</v>
       </c>
       <c r="E18">
-        <v>-27.00634024745311</v>
+        <v>-29.55348687220648</v>
       </c>
       <c r="F18">
-        <v>-1.815856875617679</v>
+        <v>-2.490382369471469</v>
       </c>
       <c r="G18">
-        <v>-7.693213304900626</v>
+        <v>-10.25286799365097</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-11.53458016812182</v>
       </c>
       <c r="E19">
-        <v>-27.6284846489969</v>
+        <v>-29.18726238649516</v>
       </c>
       <c r="F19">
-        <v>-1.812937708890213</v>
+        <v>-2.380212818368745</v>
       </c>
       <c r="G19">
-        <v>-7.367935968048193</v>
+        <v>-9.690309119727296</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-10.92369439145464</v>
       </c>
       <c r="E20">
-        <v>-27.77244936617475</v>
+        <v>-29.44065767806837</v>
       </c>
       <c r="F20">
-        <v>-1.554530154321713</v>
+        <v>-1.859894543485306</v>
       </c>
       <c r="G20">
-        <v>-7.390215462436823</v>
+        <v>-9.067802327912563</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.33041852228667</v>
       </c>
       <c r="E21">
-        <v>-28.97824614019713</v>
+        <v>-31.15051889388454</v>
       </c>
       <c r="F21">
-        <v>-1.239840004937403</v>
+        <v>-1.976951969542307</v>
       </c>
       <c r="G21">
-        <v>-6.922684046096223</v>
+        <v>-8.799831525595831</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.757819628190553</v>
       </c>
       <c r="E22">
-        <v>-30.07400778854414</v>
+        <v>-31.01285781252537</v>
       </c>
       <c r="F22">
-        <v>-1.206107227560602</v>
+        <v>-1.935779624520963</v>
       </c>
       <c r="G22">
-        <v>-6.759663115358332</v>
+        <v>-8.337031630743953</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.220640475142622</v>
       </c>
       <c r="E23">
-        <v>-29.69076076903799</v>
+        <v>-32.0456419728477</v>
       </c>
       <c r="F23">
-        <v>-1.180791491363646</v>
+        <v>-1.471925356914547</v>
       </c>
       <c r="G23">
-        <v>-6.614908745041869</v>
+        <v>-8.335253208658733</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.72273434461227</v>
       </c>
       <c r="E24">
-        <v>-30.46610571049828</v>
+        <v>-32.50505566092586</v>
       </c>
       <c r="F24">
-        <v>-1.041053365817995</v>
+        <v>-1.827801105198645</v>
       </c>
       <c r="G24">
-        <v>-5.984057806801468</v>
+        <v>-8.371668205525451</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.270969265811075</v>
       </c>
       <c r="E25">
-        <v>-30.8544721698701</v>
+        <v>-32.43061886942478</v>
       </c>
       <c r="F25">
-        <v>-0.8577083234541718</v>
+        <v>-1.583563603422433</v>
       </c>
       <c r="G25">
-        <v>-6.171425401510439</v>
+        <v>-8.714654295134206</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.871329639850458</v>
       </c>
       <c r="E26">
-        <v>-30.70957458704667</v>
+        <v>-32.90173413433876</v>
       </c>
       <c r="F26">
-        <v>-0.6865643045661828</v>
+        <v>-1.488151417600583</v>
       </c>
       <c r="G26">
-        <v>-6.025709633277059</v>
+        <v>-7.761997552451265</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.519899640467503</v>
       </c>
       <c r="E27">
-        <v>-31.00296309681861</v>
+        <v>-33.05182587684899</v>
       </c>
       <c r="F27">
-        <v>-1.019574627430806</v>
+        <v>-0.9873643893403504</v>
       </c>
       <c r="G27">
-        <v>-6.114204178735283</v>
+        <v>-8.622274783349599</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.224046616384506</v>
       </c>
       <c r="E28">
-        <v>-31.55906423343454</v>
+        <v>-33.57163808700444</v>
       </c>
       <c r="F28">
-        <v>-0.9618970619086825</v>
+        <v>-1.010996882974817</v>
       </c>
       <c r="G28">
-        <v>-6.525173897834175</v>
+        <v>-9.331251606920379</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.975062314358234</v>
       </c>
       <c r="E29">
-        <v>-31.13614098891019</v>
+        <v>-33.33907830434054</v>
       </c>
       <c r="F29">
-        <v>-0.8751032105455586</v>
+        <v>-1.373117693108622</v>
       </c>
       <c r="G29">
-        <v>-6.420210901369098</v>
+        <v>-8.389849454186333</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.771466343734314</v>
       </c>
       <c r="E30">
-        <v>-31.42391871938663</v>
+        <v>-33.11603510980375</v>
       </c>
       <c r="F30">
-        <v>-1.012290792857991</v>
+        <v>-1.38181969267503</v>
       </c>
       <c r="G30">
-        <v>-6.466791122626975</v>
+        <v>-9.003995693467601</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.601290348939279</v>
       </c>
       <c r="E31">
-        <v>-31.13889882958086</v>
+        <v>-33.94825315632636</v>
       </c>
       <c r="F31">
-        <v>-0.8648819851624155</v>
+        <v>-1.1213022863316</v>
       </c>
       <c r="G31">
-        <v>-7.07663896166537</v>
+        <v>-9.500313266549208</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.454689752510092</v>
       </c>
       <c r="E32">
-        <v>-30.16361270373391</v>
+        <v>-32.74006987650193</v>
       </c>
       <c r="F32">
-        <v>-0.9053560164631994</v>
+        <v>-0.8954512274279257</v>
       </c>
       <c r="G32">
-        <v>-6.620752600639239</v>
+        <v>-9.229169522984495</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.32377646658733</v>
       </c>
       <c r="E33">
-        <v>-30.43274444248377</v>
+        <v>-33.80766215228423</v>
       </c>
       <c r="F33">
-        <v>-0.8727804683481089</v>
+        <v>-1.11826052122852</v>
       </c>
       <c r="G33">
-        <v>-7.008583145300927</v>
+        <v>-9.752809827991598</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.197114957332467</v>
       </c>
       <c r="E34">
-        <v>-30.11231188593802</v>
+        <v>-31.68781554218362</v>
       </c>
       <c r="F34">
-        <v>-0.8798994578077678</v>
+        <v>-1.376562873136865</v>
       </c>
       <c r="G34">
-        <v>-6.901277356642406</v>
+        <v>-9.209262351783343</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.072935723049296</v>
       </c>
       <c r="E35">
-        <v>-29.75414355548635</v>
+        <v>-32.13290566697551</v>
       </c>
       <c r="F35">
-        <v>-0.8242571909943223</v>
+        <v>-1.725929310369764</v>
       </c>
       <c r="G35">
-        <v>-7.27778112448089</v>
+        <v>-9.361665249554873</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.942567815426161</v>
       </c>
       <c r="E36">
-        <v>-29.94835395601631</v>
+        <v>-31.22079175353557</v>
       </c>
       <c r="F36">
-        <v>-0.715121442410293</v>
+        <v>-1.182380300042216</v>
       </c>
       <c r="G36">
-        <v>-7.511059571249612</v>
+        <v>-8.878187096435372</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.805734196507946</v>
       </c>
       <c r="E37">
-        <v>-29.468190800035</v>
+        <v>-31.30342734722754</v>
       </c>
       <c r="F37">
-        <v>-0.6202112472345396</v>
+        <v>-1.102157058918098</v>
       </c>
       <c r="G37">
-        <v>-7.16580615754328</v>
+        <v>-9.849323678941106</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.658828915926928</v>
       </c>
       <c r="E38">
-        <v>-29.10725330772765</v>
+        <v>-30.53045985462128</v>
       </c>
       <c r="F38">
-        <v>-0.6120501715821589</v>
+        <v>-1.506699392116667</v>
       </c>
       <c r="G38">
-        <v>-7.567102835484928</v>
+        <v>-9.415296815943996</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.504048559680017</v>
       </c>
       <c r="E39">
-        <v>-28.14798213020882</v>
+        <v>-29.97693541971572</v>
       </c>
       <c r="F39">
-        <v>-0.7091944736432625</v>
+        <v>-1.577326825246756</v>
       </c>
       <c r="G39">
-        <v>-7.788549197310292</v>
+        <v>-8.830442041523892</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.346745824170526</v>
       </c>
       <c r="E40">
-        <v>-27.90380228324123</v>
+        <v>-30.24677812888478</v>
       </c>
       <c r="F40">
-        <v>-0.6846532609679243</v>
+        <v>-1.104743221949638</v>
       </c>
       <c r="G40">
-        <v>-7.712070485202755</v>
+        <v>-10.08345524331528</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.195579126065013</v>
       </c>
       <c r="E41">
-        <v>-27.02962113232654</v>
+        <v>-28.94529696331732</v>
       </c>
       <c r="F41">
-        <v>-0.4639165424091345</v>
+        <v>-1.23549521790972</v>
       </c>
       <c r="G41">
-        <v>-7.450816343418207</v>
+        <v>-10.53325165712708</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.065001994524418</v>
       </c>
       <c r="E42">
-        <v>-27.02382921407073</v>
+        <v>-29.77847278209256</v>
       </c>
       <c r="F42">
-        <v>-0.4487690160815427</v>
+        <v>-1.224467991043653</v>
       </c>
       <c r="G42">
-        <v>-7.535681857831685</v>
+        <v>-9.106140120613116</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.965062421574773</v>
       </c>
       <c r="E43">
-        <v>-26.3319961260229</v>
+        <v>-28.93713212468149</v>
       </c>
       <c r="F43">
-        <v>-0.6834670388471155</v>
+        <v>-1.445196425928415</v>
       </c>
       <c r="G43">
-        <v>-7.448063398529833</v>
+        <v>-9.933487011940862</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.910789897886129</v>
       </c>
       <c r="E44">
-        <v>-25.47936598291071</v>
+        <v>-29.09026700172488</v>
       </c>
       <c r="F44">
-        <v>-0.5422900391228013</v>
+        <v>-1.141233634410359</v>
       </c>
       <c r="G44">
-        <v>-7.339796211954395</v>
+        <v>-9.844848092734022</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.908786877333084</v>
       </c>
       <c r="E45">
-        <v>-25.14324452816538</v>
+        <v>-28.6146096773812</v>
       </c>
       <c r="F45">
-        <v>-0.560172834614437</v>
+        <v>-1.150763173012164</v>
       </c>
       <c r="G45">
-        <v>-7.709730974230871</v>
+        <v>-9.465985126594298</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.967316438867789</v>
       </c>
       <c r="E46">
-        <v>-24.63085222267149</v>
+        <v>-27.35352476419917</v>
       </c>
       <c r="F46">
-        <v>-0.4374849953206079</v>
+        <v>-1.247863571600919</v>
       </c>
       <c r="G46">
-        <v>-7.253089932246068</v>
+        <v>-9.56389021548501</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.086023144675262</v>
       </c>
       <c r="E47">
-        <v>-24.1567164655944</v>
+        <v>-27.52101943232087</v>
       </c>
       <c r="F47">
-        <v>-0.4849297383159495</v>
+        <v>-1.594053219844083</v>
       </c>
       <c r="G47">
-        <v>-8.260986039882262</v>
+        <v>-9.679523744461401</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.264299743211767</v>
       </c>
       <c r="E48">
-        <v>-23.51435242760635</v>
+        <v>-26.42785486381726</v>
       </c>
       <c r="F48">
-        <v>-0.374613566182931</v>
+        <v>-1.161605673947407</v>
       </c>
       <c r="G48">
-        <v>-8.140834268818514</v>
+        <v>-9.46467591919208</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.497691176937016</v>
       </c>
       <c r="E49">
-        <v>-22.71188419107713</v>
+        <v>-26.66531445535747</v>
       </c>
       <c r="F49">
-        <v>-0.4415406821247143</v>
+        <v>-1.397441873524426</v>
       </c>
       <c r="G49">
-        <v>-7.934593087699617</v>
+        <v>-9.072655254598981</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.775809708134574</v>
       </c>
       <c r="E50">
-        <v>-22.339276821252</v>
+        <v>-24.31065288253713</v>
       </c>
       <c r="F50">
-        <v>-0.3284072324547745</v>
+        <v>-1.151434978975834</v>
       </c>
       <c r="G50">
-        <v>-7.519872932358281</v>
+        <v>-9.329443653841125</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.093387263751474</v>
       </c>
       <c r="E51">
-        <v>-22.24517513137262</v>
+        <v>-24.68016277614101</v>
       </c>
       <c r="F51">
-        <v>-0.4277980669122705</v>
+        <v>-1.036341612030871</v>
       </c>
       <c r="G51">
-        <v>-8.127181105909665</v>
+        <v>-9.605807820906916</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.437128456706945</v>
       </c>
       <c r="E52">
-        <v>-21.43529378289283</v>
+        <v>-25.34575335731439</v>
       </c>
       <c r="F52">
-        <v>-0.3558361338962718</v>
+        <v>-1.263431908569133</v>
       </c>
       <c r="G52">
-        <v>-7.873034090022875</v>
+        <v>-9.369720648483309</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.80298297600103</v>
       </c>
       <c r="E53">
-        <v>-21.17906366659083</v>
+        <v>-24.24327824625101</v>
       </c>
       <c r="F53">
-        <v>-0.1763976722040513</v>
+        <v>-1.340882603996082</v>
       </c>
       <c r="G53">
-        <v>-7.738937127331488</v>
+        <v>-9.160713397589799</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.179481692251948</v>
       </c>
       <c r="E54">
-        <v>-20.21381943185589</v>
+        <v>-22.9859247956513</v>
       </c>
       <c r="F54">
-        <v>-0.3014157090019555</v>
+        <v>-1.271414056862509</v>
       </c>
       <c r="G54">
-        <v>-8.282845537911282</v>
+        <v>-9.486866820598605</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.561544149125301</v>
       </c>
       <c r="E55">
-        <v>-20.18840563572484</v>
+        <v>-24.23672101588791</v>
       </c>
       <c r="F55">
-        <v>-0.4577998775068629</v>
+        <v>-1.082411265137566</v>
       </c>
       <c r="G55">
-        <v>-8.864425653215061</v>
+        <v>-9.489865857103936</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.9422828945922</v>
       </c>
       <c r="E56">
-        <v>-19.61159578747184</v>
+        <v>-22.56191924583912</v>
       </c>
       <c r="F56">
-        <v>-0.5800635926904587</v>
+        <v>-1.119527923354803</v>
       </c>
       <c r="G56">
-        <v>-8.609054741686597</v>
+        <v>-8.756096123429993</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.311116034173118</v>
       </c>
       <c r="E57">
-        <v>-19.42826957421932</v>
+        <v>-22.83163968620997</v>
       </c>
       <c r="F57">
-        <v>-0.3105989900293908</v>
+        <v>-1.104556010916605</v>
       </c>
       <c r="G57">
-        <v>-8.546321066691574</v>
+        <v>-9.618870363935065</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.664684681878535</v>
       </c>
       <c r="E58">
-        <v>-18.01267312789557</v>
+        <v>-22.10183081513382</v>
       </c>
       <c r="F58">
-        <v>-0.4334152262706539</v>
+        <v>-1.268862685261887</v>
       </c>
       <c r="G58">
-        <v>-8.664235044651779</v>
+        <v>-10.32843452616499</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.991206897475276</v>
       </c>
       <c r="E59">
-        <v>-18.45797156249182</v>
+        <v>-21.72901966397835</v>
       </c>
       <c r="F59">
-        <v>-0.50752760106432</v>
+        <v>-0.9562989550005634</v>
       </c>
       <c r="G59">
-        <v>-8.726552004508752</v>
+        <v>-10.30172866389266</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.288981854117976</v>
       </c>
       <c r="E60">
-        <v>-18.16470758575509</v>
+        <v>-20.51292514006252</v>
       </c>
       <c r="F60">
-        <v>-0.5981402261543496</v>
+        <v>-1.374320482577486</v>
       </c>
       <c r="G60">
-        <v>-9.189916269468858</v>
+        <v>-9.974147909505501</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.551105690461073</v>
       </c>
       <c r="E61">
-        <v>-17.80405991578423</v>
+        <v>-22.19570155283882</v>
       </c>
       <c r="F61">
-        <v>-0.7917802186001648</v>
+        <v>-1.483659181175202</v>
       </c>
       <c r="G61">
-        <v>-9.145557435206724</v>
+        <v>-10.40510354912297</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.775115527045692</v>
       </c>
       <c r="E62">
-        <v>-17.40107554231565</v>
+        <v>-22.04406107221797</v>
       </c>
       <c r="F62">
-        <v>-0.7965565850447067</v>
+        <v>-1.170133716359228</v>
       </c>
       <c r="G62">
-        <v>-9.261492836566585</v>
+        <v>-10.06638632876305</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.96084548740243</v>
       </c>
       <c r="E63">
-        <v>-17.66936951337409</v>
+        <v>-20.55767552020632</v>
       </c>
       <c r="F63">
-        <v>-0.7265653380799681</v>
+        <v>-1.385403210059541</v>
       </c>
       <c r="G63">
-        <v>-9.81490694600409</v>
+        <v>-10.88239659960292</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.10316017104198</v>
       </c>
       <c r="E64">
-        <v>-16.99047880404018</v>
+        <v>-19.98648097972282</v>
       </c>
       <c r="F64">
-        <v>-0.7632081701428043</v>
+        <v>-1.352768019491449</v>
       </c>
       <c r="G64">
-        <v>-9.774731669230249</v>
+        <v>-10.82396132485077</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.20567793199988</v>
       </c>
       <c r="E65">
-        <v>-16.91802774839146</v>
+        <v>-20.30071179111507</v>
       </c>
       <c r="F65">
-        <v>-0.7448308393116972</v>
+        <v>-1.582572047641282</v>
       </c>
       <c r="G65">
-        <v>-9.786609691275439</v>
+        <v>-11.3387882687492</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.2653807679347</v>
       </c>
       <c r="E66">
-        <v>-17.21435750203138</v>
+        <v>-20.56490296472256</v>
       </c>
       <c r="F66">
-        <v>-0.9496190002643882</v>
+        <v>-1.613748483213044</v>
       </c>
       <c r="G66">
-        <v>-9.749164390839056</v>
+        <v>-11.76674487186134</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.2853673858175</v>
       </c>
       <c r="E67">
-        <v>-16.50214175247503</v>
+        <v>-20.95626274541345</v>
       </c>
       <c r="F67">
-        <v>-1.075803378365434</v>
+        <v>-1.99533095710822</v>
       </c>
       <c r="G67">
-        <v>-9.587915319743264</v>
+        <v>-12.51465338923493</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.26972336634196</v>
       </c>
       <c r="E68">
-        <v>-16.12800375843531</v>
+        <v>-19.74780322867455</v>
       </c>
       <c r="F68">
-        <v>-1.146681806818571</v>
+        <v>-1.869459701885432</v>
       </c>
       <c r="G68">
-        <v>-9.871265207509111</v>
+        <v>-11.93157703690004</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.21899266614865</v>
       </c>
       <c r="E69">
-        <v>-15.77697909573074</v>
+        <v>-19.98846445133819</v>
       </c>
       <c r="F69">
-        <v>-1.206472537585237</v>
+        <v>-1.737137121329642</v>
       </c>
       <c r="G69">
-        <v>-9.823792493987066</v>
+        <v>-10.47224718589389</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.13938907937285</v>
       </c>
       <c r="E70">
-        <v>-15.43549139928633</v>
+        <v>-19.28277423282688</v>
       </c>
       <c r="F70">
-        <v>-1.248622356141884</v>
+        <v>-2.040838977115816</v>
       </c>
       <c r="G70">
-        <v>-9.682279970571335</v>
+        <v>-11.09528225437969</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.02924223713833</v>
       </c>
       <c r="E71">
-        <v>-16.78133576046993</v>
+        <v>-18.64603908803037</v>
       </c>
       <c r="F71">
-        <v>-1.46659729777974</v>
+        <v>-1.838170608346889</v>
       </c>
       <c r="G71">
-        <v>-9.817768171203925</v>
+        <v>-10.8862979720371</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.894360802578802</v>
       </c>
       <c r="E72">
-        <v>-15.83933165434236</v>
+        <v>-18.47695039705797</v>
       </c>
       <c r="F72">
-        <v>-1.537655481959284</v>
+        <v>-1.867829474836723</v>
       </c>
       <c r="G72">
-        <v>-9.306652288889222</v>
+        <v>-11.53755482715568</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.737043432893456</v>
       </c>
       <c r="E73">
-        <v>-16.05770372794024</v>
+        <v>-19.17513240566456</v>
       </c>
       <c r="F73">
-        <v>-1.412778267619856</v>
+        <v>-1.967800166476178</v>
       </c>
       <c r="G73">
-        <v>-9.247701862352239</v>
+        <v>-10.88805998801452</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.560865324687054</v>
       </c>
       <c r="E74">
-        <v>-16.54638947200398</v>
+        <v>-20.423469664515</v>
       </c>
       <c r="F74">
-        <v>-1.687712580241609</v>
+        <v>-2.237775871824773</v>
       </c>
       <c r="G74">
-        <v>-9.262280329740852</v>
+        <v>-10.93324569010963</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.375750651038047</v>
       </c>
       <c r="E75">
-        <v>-16.84394644209998</v>
+        <v>-19.93838858576137</v>
       </c>
       <c r="F75">
-        <v>-1.792927665908189</v>
+        <v>-2.140441873628429</v>
       </c>
       <c r="G75">
-        <v>-9.478788453119252</v>
+        <v>-11.16109371519747</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.183358634465929</v>
       </c>
       <c r="E76">
-        <v>-16.84757827825413</v>
+        <v>-19.8462477251273</v>
       </c>
       <c r="F76">
-        <v>-1.712555318651567</v>
+        <v>-2.59624026824262</v>
       </c>
       <c r="G76">
-        <v>-8.735234116755043</v>
+        <v>-10.19723160088903</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.99205836910455</v>
       </c>
       <c r="E77">
-        <v>-16.89691147409369</v>
+        <v>-21.62281789155046</v>
       </c>
       <c r="F77">
-        <v>-1.942672469679658</v>
+        <v>-2.295413675711563</v>
       </c>
       <c r="G77">
-        <v>-8.455943100058228</v>
+        <v>-10.4657011488828</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.800288374246536</v>
       </c>
       <c r="E78">
-        <v>-17.52224392133888</v>
+        <v>-20.62594679434596</v>
       </c>
       <c r="F78">
-        <v>-1.884333038602697</v>
+        <v>-2.925096328582204</v>
       </c>
       <c r="G78">
-        <v>-8.399430621139912</v>
+        <v>-10.56520419267296</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.609349929966777</v>
       </c>
       <c r="E79">
-        <v>-17.57829284413182</v>
+        <v>-20.84046966503731</v>
       </c>
       <c r="F79">
-        <v>-1.883721703459431</v>
+        <v>-2.552828017764107</v>
       </c>
       <c r="G79">
-        <v>-8.432643145764612</v>
+        <v>-10.42452181831176</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.417569647063438</v>
       </c>
       <c r="E80">
-        <v>-18.42362761561765</v>
+        <v>-22.0623244078909</v>
       </c>
       <c r="F80">
-        <v>-2.071102551809693</v>
+        <v>-2.881215222153706</v>
       </c>
       <c r="G80">
-        <v>-7.609942464165038</v>
+        <v>-9.941056790078502</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.218586364464947</v>
       </c>
       <c r="E81">
-        <v>-18.54254081458507</v>
+        <v>-21.97108924205837</v>
       </c>
       <c r="F81">
-        <v>-2.021465120299141</v>
+        <v>-2.638863084586266</v>
       </c>
       <c r="G81">
-        <v>-7.82478044576968</v>
+        <v>-9.89899152968642</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.013366030628083</v>
       </c>
       <c r="E82">
-        <v>-19.23815517842931</v>
+        <v>-23.06577537782855</v>
       </c>
       <c r="F82">
-        <v>-2.062513210210065</v>
+        <v>-2.922939259865315</v>
       </c>
       <c r="G82">
-        <v>-7.294006765092344</v>
+        <v>-8.985364917453074</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.79415944387762</v>
       </c>
       <c r="E83">
-        <v>-20.50745927193526</v>
+        <v>-22.63745872076107</v>
       </c>
       <c r="F83">
-        <v>-2.06588797900907</v>
+        <v>-2.974103372499226</v>
       </c>
       <c r="G83">
-        <v>-7.001147897247225</v>
+        <v>-9.286764805017429</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.562853219925083</v>
       </c>
       <c r="E84">
-        <v>-20.91383094396157</v>
+        <v>-23.47245045761338</v>
       </c>
       <c r="F84">
-        <v>-2.204960097162871</v>
+        <v>-2.455240539142505</v>
       </c>
       <c r="G84">
-        <v>-7.156664674278667</v>
+        <v>-9.385982382531918</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.316697726031154</v>
       </c>
       <c r="E85">
-        <v>-22.31975004133093</v>
+        <v>-24.78670418411947</v>
       </c>
       <c r="F85">
-        <v>-2.257914311754232</v>
+        <v>-3.127830138375953</v>
       </c>
       <c r="G85">
-        <v>-6.457216518116515</v>
+        <v>-8.828722681426743</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.058481322241858</v>
       </c>
       <c r="E86">
-        <v>-22.82946601868629</v>
+        <v>-26.20605473539558</v>
       </c>
       <c r="F86">
-        <v>-2.224011719059857</v>
+        <v>-3.251138424854479</v>
       </c>
       <c r="G86">
-        <v>-6.633411553415577</v>
+        <v>-8.235691102880502</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.794226906361582</v>
       </c>
       <c r="E87">
-        <v>-23.60738539761994</v>
+        <v>-27.01792861243873</v>
       </c>
       <c r="F87">
-        <v>-2.398232294481843</v>
+        <v>-2.953466255393282</v>
       </c>
       <c r="G87">
-        <v>-5.755451819533395</v>
+        <v>-8.451244390785103</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.530481204364612</v>
       </c>
       <c r="E88">
-        <v>-25.36409367704546</v>
+        <v>-27.8842392755281</v>
       </c>
       <c r="F88">
-        <v>-2.569660443388992</v>
+        <v>-3.144510144398724</v>
       </c>
       <c r="G88">
-        <v>-5.931328576341191</v>
+        <v>-8.74299420574313</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.282699008403096</v>
       </c>
       <c r="E89">
-        <v>-26.47424455155184</v>
+        <v>-30.11216018205876</v>
       </c>
       <c r="F89">
-        <v>-2.591972519383397</v>
+        <v>-3.175463749139133</v>
       </c>
       <c r="G89">
-        <v>-6.395736269757199</v>
+        <v>-7.37492496996981</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.061029265584393</v>
       </c>
       <c r="E90">
-        <v>-28.42661460742677</v>
+        <v>-30.48725821258811</v>
       </c>
       <c r="F90">
-        <v>-2.4257970481774</v>
+        <v>-3.278500228536349</v>
       </c>
       <c r="G90">
-        <v>-5.421466120662196</v>
+        <v>-8.759797341349048</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.88397077491762</v>
       </c>
       <c r="E91">
-        <v>-29.56166529626433</v>
+        <v>-32.42904748894412</v>
       </c>
       <c r="F91">
-        <v>-2.714580007039155</v>
+        <v>-3.603571478212542</v>
       </c>
       <c r="G91">
-        <v>-5.463446069293732</v>
+        <v>-7.622571885947341</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.762708611435778</v>
       </c>
       <c r="E92">
-        <v>-30.58030703226071</v>
+        <v>-33.8645035580285</v>
       </c>
       <c r="F92">
-        <v>-2.832645556225363</v>
+        <v>-3.434803217035782</v>
       </c>
       <c r="G92">
-        <v>-5.75820148320021</v>
+        <v>-7.462061089702424</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.711605213797378</v>
       </c>
       <c r="E93">
-        <v>-32.54840674260129</v>
+        <v>-34.45713589446431</v>
       </c>
       <c r="F93">
-        <v>-2.83847974784328</v>
+        <v>-3.979808497257452</v>
       </c>
       <c r="G93">
-        <v>-5.733024670174591</v>
+        <v>-8.29526496151378</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.737757050264036</v>
       </c>
       <c r="E94">
-        <v>-34.1079769630509</v>
+        <v>-36.6594505447186</v>
       </c>
       <c r="F94">
-        <v>-3.133358662422236</v>
+        <v>-3.909133847185404</v>
       </c>
       <c r="G94">
-        <v>-5.69485750099513</v>
+        <v>-8.194524897195709</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.844110375394053</v>
       </c>
       <c r="E95">
-        <v>-35.72378856643877</v>
+        <v>-38.36885664889701</v>
       </c>
       <c r="F95">
-        <v>-3.169448973427405</v>
+        <v>-3.756935419166843</v>
       </c>
       <c r="G95">
-        <v>-6.590299583346033</v>
+        <v>-8.844190359857965</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.0339471988018</v>
       </c>
       <c r="E96">
-        <v>-37.96595831643457</v>
+        <v>-40.34789488820311</v>
       </c>
       <c r="F96">
-        <v>-3.327754125939405</v>
+        <v>-4.118934459292436</v>
       </c>
       <c r="G96">
-        <v>-6.303396132631306</v>
+        <v>-8.839288214848155</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.291739019608832</v>
       </c>
       <c r="E97">
-        <v>-40.19179386068471</v>
+        <v>-42.77021865540906</v>
       </c>
       <c r="F97">
-        <v>-3.329886343634211</v>
+        <v>-4.250315186111242</v>
       </c>
       <c r="G97">
-        <v>-7.127153367573021</v>
+        <v>-8.83919634064449</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.618195408625168</v>
       </c>
       <c r="E98">
-        <v>-41.5526886052328</v>
+        <v>-44.44217654378103</v>
       </c>
       <c r="F98">
-        <v>-3.317300957683478</v>
+        <v>-3.830287352684739</v>
       </c>
       <c r="G98">
-        <v>-6.782926976214795</v>
+        <v>-8.387388538016751</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.979979266432177</v>
       </c>
       <c r="E99">
-        <v>-43.57450507425236</v>
+        <v>-45.59993752976705</v>
       </c>
       <c r="F99">
-        <v>-3.543929025210978</v>
+        <v>-4.796930812563954</v>
       </c>
       <c r="G99">
-        <v>-7.314806428557664</v>
+        <v>-9.686581652035766</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.385287828758348</v>
       </c>
       <c r="E100">
-        <v>-46.30070529703202</v>
+        <v>-47.38756396547995</v>
       </c>
       <c r="F100">
-        <v>-3.686502652376412</v>
+        <v>-4.715704418515046</v>
       </c>
       <c r="G100">
-        <v>-7.688803343124732</v>
+        <v>-9.338598261991976</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.778812089247004</v>
       </c>
       <c r="E101">
-        <v>-47.90437832584233</v>
+        <v>-49.52730416189625</v>
       </c>
       <c r="F101">
-        <v>-3.763429819604791</v>
+        <v>-4.597338171961622</v>
       </c>
       <c r="G101">
-        <v>-7.997343168802438</v>
+        <v>-9.937089793213133</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.207469419676874</v>
       </c>
       <c r="E102">
-        <v>-50.20365213307485</v>
+        <v>-50.85100315306384</v>
       </c>
       <c r="F102">
-        <v>-4.112577567843352</v>
+        <v>-5.117673014193118</v>
       </c>
       <c r="G102">
-        <v>-7.892307985463053</v>
+        <v>-10.3434986143444</v>
       </c>
     </row>
   </sheetData>
